--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127451704</v>
       </c>
       <c r="B2" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127451822</v>
       </c>
       <c r="B3" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127451748</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127451808</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R5" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R6" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R5" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R6" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127451704</v>
       </c>
       <c r="B2" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127451822</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127451748</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R5" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R6" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,7 +1168,7 @@
         <v>127451808</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R5" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R6" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R5" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R6" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127451704</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127451822</v>
       </c>
       <c r="B3" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127451748</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127451808</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127451704</v>
       </c>
       <c r="B2" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127451822</v>
       </c>
       <c r="B3" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127451748</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127451808</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R5" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R6" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451907</v>
+        <v>127451840</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499214</v>
+        <v>499256</v>
       </c>
       <c r="R5" t="n">
-        <v>6846760</v>
+        <v>6846791</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451840</v>
+        <v>127451907</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499256</v>
+        <v>499214</v>
       </c>
       <c r="R6" t="n">
-        <v>6846791</v>
+        <v>6846760</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>127451907</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>127451907</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127451704</v>
       </c>
       <c r="B2" t="n">
-        <v>80133</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127451822</v>
       </c>
       <c r="B3" t="n">
-        <v>80133</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,11 +872,11 @@
         <v>127451748</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127451907</v>
+        <v>127452136</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499214</v>
+        <v>499194</v>
       </c>
       <c r="R5" t="n">
-        <v>6846760</v>
+        <v>6846561</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127451840</v>
+        <v>127451808</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499256</v>
+        <v>499263</v>
       </c>
       <c r="R6" t="n">
-        <v>6846791</v>
+        <v>6846797</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127451808</v>
+        <v>127451840</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499263</v>
+        <v>499256</v>
       </c>
       <c r="R7" t="n">
-        <v>6846797</v>
+        <v>6846791</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1259,6 +1254,108 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127451907</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499214</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846760</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36150-2025 artfynd.xlsx
+++ b/artfynd/A 36150-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127452136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,8 +1391,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127451907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>